--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/15.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/15.xlsx
@@ -426,13 +426,13 @@
         <v>-5.407098678711826</v>
       </c>
       <c r="E2">
-        <v>-5.982809097363318</v>
+        <v>-6.638427978771809</v>
       </c>
       <c r="F2">
-        <v>-3.961654825625101</v>
+        <v>-3.84905650129737</v>
       </c>
       <c r="G2">
-        <v>-8.661652909797761</v>
+        <v>-8.417672324644553</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.202171773896394</v>
       </c>
       <c r="E3">
-        <v>-6.617990975575193</v>
+        <v>-7.079759470137339</v>
       </c>
       <c r="F3">
-        <v>-3.690980806555946</v>
+        <v>-3.70878904898133</v>
       </c>
       <c r="G3">
-        <v>-9.173718162175611</v>
+        <v>-8.782696386350134</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.23617130325101</v>
       </c>
       <c r="E4">
-        <v>-7.928866460471562</v>
+        <v>-7.593560131047618</v>
       </c>
       <c r="F4">
-        <v>-3.847911697546701</v>
+        <v>-3.373595149642927</v>
       </c>
       <c r="G4">
-        <v>-8.369106621583445</v>
+        <v>-8.007578495967335</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.386309107761079</v>
       </c>
       <c r="E5">
-        <v>-7.254083077062609</v>
+        <v>-7.845008178797523</v>
       </c>
       <c r="F5">
-        <v>-3.727011475108113</v>
+        <v>-3.564951333159224</v>
       </c>
       <c r="G5">
-        <v>-7.762862969704408</v>
+        <v>-7.719193563495883</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.635711491583002</v>
       </c>
       <c r="E6">
-        <v>-7.900427643703392</v>
+        <v>-9.390254835960871</v>
       </c>
       <c r="F6">
-        <v>-3.735962813262765</v>
+        <v>-3.488446633306272</v>
       </c>
       <c r="G6">
-        <v>-8.307752281104131</v>
+        <v>-7.904703293334483</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.92868522512526</v>
       </c>
       <c r="E7">
-        <v>-9.790413441648662</v>
+        <v>-10.15361969943386</v>
       </c>
       <c r="F7">
-        <v>-3.798734838312106</v>
+        <v>-3.124806597355735</v>
       </c>
       <c r="G7">
-        <v>-7.301786739722414</v>
+        <v>-8.195938605515247</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.23319841446736</v>
       </c>
       <c r="E8">
-        <v>-9.775854397714001</v>
+        <v>-9.532344764899543</v>
       </c>
       <c r="F8">
-        <v>-3.426208076864334</v>
+        <v>-3.263812446117311</v>
       </c>
       <c r="G8">
-        <v>-7.680893862152054</v>
+        <v>-7.337623395185024</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.49585641574406</v>
       </c>
       <c r="E9">
-        <v>-10.48696519961249</v>
+        <v>-10.46461265191062</v>
       </c>
       <c r="F9">
-        <v>-3.454534928570467</v>
+        <v>-3.123419910323448</v>
       </c>
       <c r="G9">
-        <v>-6.864513332167779</v>
+        <v>-8.19851752049034</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.66821780295609</v>
       </c>
       <c r="E10">
-        <v>-10.97838161350285</v>
+        <v>-11.85359072801728</v>
       </c>
       <c r="F10">
-        <v>-3.47602112226428</v>
+        <v>-3.068840438887794</v>
       </c>
       <c r="G10">
-        <v>-6.717482073132128</v>
+        <v>-7.886270175771821</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.68993472640848</v>
       </c>
       <c r="E11">
-        <v>-13.21493605572914</v>
+        <v>-12.3010537731892</v>
       </c>
       <c r="F11">
-        <v>-3.429427112591613</v>
+        <v>-2.834460509204896</v>
       </c>
       <c r="G11">
-        <v>-6.820512871405326</v>
+        <v>-7.980094346900305</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.5084164943869</v>
       </c>
       <c r="E12">
-        <v>-12.23040957866954</v>
+        <v>-12.49269879319381</v>
       </c>
       <c r="F12">
-        <v>-3.101070557795917</v>
+        <v>-2.511136286381208</v>
       </c>
       <c r="G12">
-        <v>-6.474934954197424</v>
+        <v>-6.801401092007113</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-17.07178635240373</v>
       </c>
       <c r="E13">
-        <v>-12.15567617212096</v>
+        <v>-13.34475834858103</v>
       </c>
       <c r="F13">
-        <v>-2.779895948382493</v>
+        <v>-2.541357614337542</v>
       </c>
       <c r="G13">
-        <v>-5.985315200575833</v>
+        <v>-6.407555420836638</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.34194112992106</v>
       </c>
       <c r="E14">
-        <v>-14.3238959415715</v>
+        <v>-13.99544572179517</v>
       </c>
       <c r="F14">
-        <v>-2.731586389818629</v>
+        <v>-1.95251181769011</v>
       </c>
       <c r="G14">
-        <v>-5.294149434523413</v>
+        <v>-6.230543861397347</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.29484507380648</v>
       </c>
       <c r="E15">
-        <v>-14.03973419759019</v>
+        <v>-13.73634455297231</v>
       </c>
       <c r="F15">
-        <v>-2.636112076441569</v>
+        <v>-2.011357381250182</v>
       </c>
       <c r="G15">
-        <v>-5.16824938766493</v>
+        <v>-5.856091365995922</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.92254231325142</v>
       </c>
       <c r="E16">
-        <v>-15.41498194050559</v>
+        <v>-14.74941853017626</v>
       </c>
       <c r="F16">
-        <v>-2.079768931577782</v>
+        <v>-1.727904138258038</v>
       </c>
       <c r="G16">
-        <v>-4.104091076793903</v>
+        <v>-5.627051272861445</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.23578380463513</v>
       </c>
       <c r="E17">
-        <v>-15.36484267629266</v>
+        <v>-15.78198305950922</v>
       </c>
       <c r="F17">
-        <v>-1.999350195746603</v>
+        <v>-1.665900838158495</v>
       </c>
       <c r="G17">
-        <v>-3.796379179464186</v>
+        <v>-4.281725018794577</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.26164236881946</v>
       </c>
       <c r="E18">
-        <v>-15.82173400434855</v>
+        <v>-16.72024664610646</v>
       </c>
       <c r="F18">
-        <v>-1.373835887646849</v>
+        <v>-1.080253368053273</v>
       </c>
       <c r="G18">
-        <v>-3.748012109135433</v>
+        <v>-4.534971820912205</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.04989442057726</v>
       </c>
       <c r="E19">
-        <v>-17.33447527508484</v>
+        <v>-16.94091012755222</v>
       </c>
       <c r="F19">
-        <v>-1.159498307274685</v>
+        <v>-0.7448788846210596</v>
       </c>
       <c r="G19">
-        <v>-3.550395714259718</v>
+        <v>-4.137136942366908</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.66661520948312</v>
       </c>
       <c r="E20">
-        <v>-18.70303446189092</v>
+        <v>-18.31048822101002</v>
       </c>
       <c r="F20">
-        <v>-1.286509396043725</v>
+        <v>-0.7453750766953365</v>
       </c>
       <c r="G20">
-        <v>-3.461328797071166</v>
+        <v>-4.463123051073403</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.192474659619</v>
       </c>
       <c r="E21">
-        <v>-18.97128314820928</v>
+        <v>-18.56473033722265</v>
       </c>
       <c r="F21">
-        <v>-0.8873332268804905</v>
+        <v>-0.2348091712450556</v>
       </c>
       <c r="G21">
-        <v>-3.855714087164543</v>
+        <v>-4.07403463384286</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.712020535303004</v>
       </c>
       <c r="E22">
-        <v>-19.60688617450386</v>
+        <v>-19.44384752480571</v>
       </c>
       <c r="F22">
-        <v>-0.7112421978629828</v>
+        <v>0.3472166765751274</v>
       </c>
       <c r="G22">
-        <v>-3.275133784305937</v>
+        <v>-3.709758755429155</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.312755772807323</v>
       </c>
       <c r="E23">
-        <v>-19.59021686168163</v>
+        <v>-20.03247216174472</v>
       </c>
       <c r="F23">
-        <v>-0.9666286965134733</v>
+        <v>-0.2281664930420064</v>
       </c>
       <c r="G23">
-        <v>-2.92358364294519</v>
+        <v>-4.048440806278754</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.069990288480291</v>
       </c>
       <c r="E24">
-        <v>-19.76884251891419</v>
+        <v>-20.70033150839595</v>
       </c>
       <c r="F24">
-        <v>-0.435579750294169</v>
+        <v>0.3695966786965617</v>
       </c>
       <c r="G24">
-        <v>-3.86254043206652</v>
+        <v>-3.845342147990007</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.038341022520564</v>
       </c>
       <c r="E25">
-        <v>-20.3062818141445</v>
+        <v>-20.8869816215701</v>
       </c>
       <c r="F25">
-        <v>-0.4877329336070231</v>
+        <v>0.2244087240078923</v>
       </c>
       <c r="G25">
-        <v>-3.826968620247051</v>
+        <v>-4.687455548451036</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.253621947200068</v>
       </c>
       <c r="E26">
-        <v>-20.78359655997498</v>
+        <v>-20.54263192955284</v>
       </c>
       <c r="F26">
-        <v>-0.461113347118061</v>
+        <v>0.1330455980509264</v>
       </c>
       <c r="G26">
-        <v>-3.138918077547085</v>
+        <v>-3.930277504345548</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.727564208685059</v>
       </c>
       <c r="E27">
-        <v>-20.97076291918601</v>
+        <v>-20.74501396142963</v>
       </c>
       <c r="F27">
-        <v>-0.3772925063635846</v>
+        <v>0.1623822296210709</v>
       </c>
       <c r="G27">
-        <v>-4.604059595771256</v>
+        <v>-4.498598857072232</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.458358766422856</v>
       </c>
       <c r="E28">
-        <v>-21.24444124583956</v>
+        <v>-21.2841378489908</v>
       </c>
       <c r="F28">
-        <v>-0.05895008510033177</v>
+        <v>0.03280403027075547</v>
       </c>
       <c r="G28">
-        <v>-4.908004092277283</v>
+        <v>-4.258167176737123</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.423728674772299</v>
       </c>
       <c r="E29">
-        <v>-21.11399402357461</v>
+        <v>-20.86662160243161</v>
       </c>
       <c r="F29">
-        <v>-0.2544331950173759</v>
+        <v>-0.06078409053012988</v>
       </c>
       <c r="G29">
-        <v>-3.735647221546256</v>
+        <v>-4.560628548841557</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.588073180188101</v>
       </c>
       <c r="E30">
-        <v>-21.34817499993327</v>
+        <v>-20.84649706394152</v>
       </c>
       <c r="F30">
-        <v>-0.6105276322958134</v>
+        <v>-0.1203876102637627</v>
       </c>
       <c r="G30">
-        <v>-4.249241945963249</v>
+        <v>-4.524705819194925</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.906547112890983</v>
       </c>
       <c r="E31">
-        <v>-19.6637638080402</v>
+        <v>-20.86688425392406</v>
       </c>
       <c r="F31">
-        <v>-0.5908646752555615</v>
+        <v>-0.451730429546551</v>
       </c>
       <c r="G31">
-        <v>-4.02243316052224</v>
+        <v>-4.371434181817747</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.332964569629277</v>
       </c>
       <c r="E32">
-        <v>-21.15458273610536</v>
+        <v>-21.39675194061355</v>
       </c>
       <c r="F32">
-        <v>-0.8383038170435935</v>
+        <v>-0.4666352442251225</v>
       </c>
       <c r="G32">
-        <v>-4.344526067674551</v>
+        <v>-4.553560534115213</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.827486089216198</v>
       </c>
       <c r="E33">
-        <v>-20.26200692377151</v>
+        <v>-19.87401179926832</v>
       </c>
       <c r="F33">
-        <v>-0.7415115711286796</v>
+        <v>-0.4615076500017935</v>
       </c>
       <c r="G33">
-        <v>-4.266979848962663</v>
+        <v>-4.191780807038119</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.35551056731729</v>
       </c>
       <c r="E34">
-        <v>-18.99832266650908</v>
+        <v>-19.75860363918284</v>
       </c>
       <c r="F34">
-        <v>-0.9105349694655019</v>
+        <v>-0.3124644734204953</v>
       </c>
       <c r="G34">
-        <v>-3.958225129788075</v>
+        <v>-3.670131525324079</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.891520272902848</v>
       </c>
       <c r="E35">
-        <v>-19.81880970111482</v>
+        <v>-19.20886048007369</v>
       </c>
       <c r="F35">
-        <v>-0.3135744857402466</v>
+        <v>-0.3665701187017478</v>
       </c>
       <c r="G35">
-        <v>-4.805532776200222</v>
+        <v>-3.988579521837653</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.412648188936491</v>
       </c>
       <c r="E36">
-        <v>-19.75169318784714</v>
+        <v>-19.76528313834416</v>
       </c>
       <c r="F36">
-        <v>-0.2541291841805485</v>
+        <v>-0.6064437810000118</v>
       </c>
       <c r="G36">
-        <v>-3.579091522994121</v>
+        <v>-3.783203208217886</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.903241296155675</v>
       </c>
       <c r="E37">
-        <v>-19.31485394269722</v>
+        <v>-19.02610485454613</v>
       </c>
       <c r="F37">
-        <v>-0.6356180525592076</v>
+        <v>-0.3459255462891785</v>
       </c>
       <c r="G37">
-        <v>-4.114751033430356</v>
+        <v>-3.728648728276236</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.35030599301024</v>
       </c>
       <c r="E38">
-        <v>-18.32580804857797</v>
+        <v>-18.89413153654059</v>
       </c>
       <c r="F38">
-        <v>-0.3580188820026485</v>
+        <v>-0.4341069130519914</v>
       </c>
       <c r="G38">
-        <v>-3.888898995650197</v>
+        <v>-3.333359659250639</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.741239438800029</v>
       </c>
       <c r="E39">
-        <v>-17.96788199148571</v>
+        <v>-18.93538593475047</v>
       </c>
       <c r="F39">
-        <v>-0.3284188295984137</v>
+        <v>-0.5460740214187895</v>
       </c>
       <c r="G39">
-        <v>-4.07098893194673</v>
+        <v>-2.559933457638408</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.068228698001077</v>
       </c>
       <c r="E40">
-        <v>-18.28240262521444</v>
+        <v>-18.10214218886512</v>
       </c>
       <c r="F40">
-        <v>-0.5970931697572111</v>
+        <v>-0.6230343233432803</v>
       </c>
       <c r="G40">
-        <v>-3.234817960728693</v>
+        <v>-3.18122684953897</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.323116122007793</v>
       </c>
       <c r="E41">
-        <v>-17.05427594586024</v>
+        <v>-17.77078921724987</v>
       </c>
       <c r="F41">
-        <v>-0.6004488861059518</v>
+        <v>-0.4000626695317374</v>
       </c>
       <c r="G41">
-        <v>-3.049672390899412</v>
+        <v>-2.826220498635225</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.501212027406337</v>
       </c>
       <c r="E42">
-        <v>-15.72907689767761</v>
+        <v>-17.64342588578414</v>
       </c>
       <c r="F42">
-        <v>-0.862901358702322</v>
+        <v>-0.6582283408186201</v>
       </c>
       <c r="G42">
-        <v>-3.323398227722972</v>
+        <v>-2.701379826349308</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.598626551005047</v>
       </c>
       <c r="E43">
-        <v>-16.42345045964374</v>
+        <v>-16.97169922233037</v>
       </c>
       <c r="F43">
-        <v>-0.5946685383692168</v>
+        <v>-0.5192995302255038</v>
       </c>
       <c r="G43">
-        <v>-3.823403162701256</v>
+        <v>-2.712049714622379</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.614599557192422</v>
       </c>
       <c r="E44">
-        <v>-16.86006780956729</v>
+        <v>-16.69869563830395</v>
       </c>
       <c r="F44">
-        <v>-0.637277272467015</v>
+        <v>-0.7306135695774493</v>
       </c>
       <c r="G44">
-        <v>-3.174287946088658</v>
+        <v>-2.997435292835252</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.550074952232363</v>
       </c>
       <c r="E45">
-        <v>-15.48214373851335</v>
+        <v>-15.16356559207374</v>
       </c>
       <c r="F45">
-        <v>-1.01374043581289</v>
+        <v>-0.695566173132405</v>
       </c>
       <c r="G45">
-        <v>-2.701982345637456</v>
+        <v>-2.528473343378713</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.412094989056284</v>
       </c>
       <c r="E46">
-        <v>-15.84826180508548</v>
+        <v>-15.73519486606197</v>
       </c>
       <c r="F46">
-        <v>-0.869123226264749</v>
+        <v>-0.5726944362751544</v>
       </c>
       <c r="G46">
-        <v>-2.895943898237815</v>
+        <v>-2.543738268860293</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.212431068835151</v>
       </c>
       <c r="E47">
-        <v>-15.07951711449138</v>
+        <v>-15.60633713817371</v>
       </c>
       <c r="F47">
-        <v>-1.068827696466459</v>
+        <v>-1.003347738377367</v>
       </c>
       <c r="G47">
-        <v>-3.305193537802519</v>
+        <v>-3.077457799610515</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.965478739843199</v>
       </c>
       <c r="E48">
-        <v>-14.60145517044963</v>
+        <v>-14.86443271302307</v>
       </c>
       <c r="F48">
-        <v>-0.8493426410532996</v>
+        <v>-1.202762279988097</v>
       </c>
       <c r="G48">
-        <v>-3.255508870349137</v>
+        <v>-2.258786372113065</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.691202776292242</v>
       </c>
       <c r="E49">
-        <v>-13.46054237200915</v>
+        <v>-14.87979782533109</v>
       </c>
       <c r="F49">
-        <v>-1.315498941672096</v>
+        <v>-1.069128393833676</v>
       </c>
       <c r="G49">
-        <v>-2.925997030643319</v>
+        <v>-2.833871169376481</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.407788814798517</v>
       </c>
       <c r="E50">
-        <v>-13.21614515828919</v>
+        <v>-14.80030952107446</v>
       </c>
       <c r="F50">
-        <v>-1.207410249485205</v>
+        <v>-1.127935024125815</v>
       </c>
       <c r="G50">
-        <v>-3.808889731057091</v>
+        <v>-2.683744550261611</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.136237311895639</v>
       </c>
       <c r="E51">
-        <v>-13.81355503480308</v>
+        <v>-14.13856814280759</v>
       </c>
       <c r="F51">
-        <v>-1.369490272251762</v>
+        <v>-1.463804871264903</v>
       </c>
       <c r="G51">
-        <v>-3.185722570381301</v>
+        <v>-2.648689183546268</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.894614116264831</v>
       </c>
       <c r="E52">
-        <v>-13.00205702110256</v>
+        <v>-14.07450834949509</v>
       </c>
       <c r="F52">
-        <v>-1.332134215855116</v>
+        <v>-1.253411976464871</v>
       </c>
       <c r="G52">
-        <v>-2.563680995188863</v>
+        <v>-2.866503216757077</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.699782890021003</v>
       </c>
       <c r="E53">
-        <v>-13.36680296005037</v>
+        <v>-12.96472880985734</v>
       </c>
       <c r="F53">
-        <v>-1.401234967861845</v>
+        <v>-1.243012652090125</v>
       </c>
       <c r="G53">
-        <v>-2.855045418645659</v>
+        <v>-2.791228032285129</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.567493772232089</v>
       </c>
       <c r="E54">
-        <v>-13.06378917877513</v>
+        <v>-13.44953818017051</v>
       </c>
       <c r="F54">
-        <v>-1.26125910087159</v>
+        <v>-1.624912390700573</v>
       </c>
       <c r="G54">
-        <v>-2.570954263738642</v>
+        <v>-3.232080139567715</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.51111834818749</v>
       </c>
       <c r="E55">
-        <v>-11.46987048297734</v>
+        <v>-12.55814882802667</v>
       </c>
       <c r="F55">
-        <v>-1.616043889286202</v>
+        <v>-1.392878397502404</v>
       </c>
       <c r="G55">
-        <v>-3.486604812263502</v>
+        <v>-3.308000880419821</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.540981120247608</v>
       </c>
       <c r="E56">
-        <v>-11.9194302116148</v>
+        <v>-12.85692848610474</v>
       </c>
       <c r="F56">
-        <v>-1.366376439184639</v>
+        <v>-1.688710762961983</v>
       </c>
       <c r="G56">
-        <v>-3.912043019515242</v>
+        <v>-3.156450726723065</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.660343269429924</v>
       </c>
       <c r="E57">
-        <v>-10.94663248223507</v>
+        <v>-11.79011057937776</v>
       </c>
       <c r="F57">
-        <v>-1.743840270353095</v>
+        <v>-1.434737459100668</v>
       </c>
       <c r="G57">
-        <v>-3.955358197351067</v>
+        <v>-3.350087845860576</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.872045705852553</v>
       </c>
       <c r="E58">
-        <v>-10.59275488090567</v>
+        <v>-12.48937489327218</v>
       </c>
       <c r="F58">
-        <v>-1.192473956845328</v>
+        <v>-1.65045924140291</v>
       </c>
       <c r="G58">
-        <v>-3.754944391494667</v>
+        <v>-3.520703431317995</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.173145547900747</v>
       </c>
       <c r="E59">
-        <v>-10.24891237797727</v>
+        <v>-11.7856455040062</v>
       </c>
       <c r="F59">
-        <v>-1.308119016480555</v>
+        <v>-1.674516687515013</v>
       </c>
       <c r="G59">
-        <v>-4.08302938607306</v>
+        <v>-3.30305823592969</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.561460376604256</v>
       </c>
       <c r="E60">
-        <v>-9.992406024760799</v>
+        <v>-11.06344446926293</v>
       </c>
       <c r="F60">
-        <v>-1.647733084280297</v>
+        <v>-1.878488078208544</v>
       </c>
       <c r="G60">
-        <v>-3.863963966648407</v>
+        <v>-3.969997429725724</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.027726452830134</v>
       </c>
       <c r="E61">
-        <v>-10.13180604013892</v>
+        <v>-10.40994944216404</v>
       </c>
       <c r="F61">
-        <v>-1.807308124020788</v>
+        <v>-1.943176945427963</v>
       </c>
       <c r="G61">
-        <v>-4.477772215084678</v>
+        <v>-4.097142241706972</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.556329484386078</v>
       </c>
       <c r="E62">
-        <v>-9.441585088837813</v>
+        <v>-10.46919546760639</v>
       </c>
       <c r="F62">
-        <v>-1.614064919560914</v>
+        <v>-1.980715242653225</v>
       </c>
       <c r="G62">
-        <v>-4.244368822929441</v>
+        <v>-4.10120097053812</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.13361533125599</v>
       </c>
       <c r="E63">
-        <v>-10.41157063585878</v>
+        <v>-11.00349200187538</v>
       </c>
       <c r="F63">
-        <v>-1.840199280116345</v>
+        <v>-1.873398588885744</v>
       </c>
       <c r="G63">
-        <v>-5.091739369706834</v>
+        <v>-4.594502050799379</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.7416415106013</v>
       </c>
       <c r="E64">
-        <v>-9.508067615744423</v>
+        <v>-10.48737276227317</v>
       </c>
       <c r="F64">
-        <v>-1.911894478828642</v>
+        <v>-2.04653897321448</v>
       </c>
       <c r="G64">
-        <v>-4.632990453238946</v>
+        <v>-4.434645738344591</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.36317431484733</v>
       </c>
       <c r="E65">
-        <v>-8.722703425542168</v>
+        <v>-10.11710208503601</v>
       </c>
       <c r="F65">
-        <v>-2.160205063124419</v>
+        <v>-2.05709982923277</v>
       </c>
       <c r="G65">
-        <v>-4.567027833368968</v>
+        <v>-4.868383483263285</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.97771129805882</v>
       </c>
       <c r="E66">
-        <v>-9.023815247734193</v>
+        <v>-10.53057893278036</v>
       </c>
       <c r="F66">
-        <v>-1.828464627488287</v>
+        <v>-2.253266342257124</v>
       </c>
       <c r="G66">
-        <v>-4.867853795977002</v>
+        <v>-4.619357626708227</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.57006470083464</v>
       </c>
       <c r="E67">
-        <v>-8.06950727772778</v>
+        <v>-10.02886024052254</v>
       </c>
       <c r="F67">
-        <v>-1.96660814578355</v>
+        <v>-1.845789103350436</v>
       </c>
       <c r="G67">
-        <v>-5.197051133856589</v>
+        <v>-4.638747491931739</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.12628779495777</v>
       </c>
       <c r="E68">
-        <v>-9.258643795875948</v>
+        <v>-10.28107360037975</v>
       </c>
       <c r="F68">
-        <v>-2.362444337578696</v>
+        <v>-1.833936822551181</v>
       </c>
       <c r="G68">
-        <v>-5.058220096121713</v>
+        <v>-4.808293771179974</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.63647849397991</v>
       </c>
       <c r="E69">
-        <v>-8.232894619924526</v>
+        <v>-9.141415189239384</v>
       </c>
       <c r="F69">
-        <v>-1.694664239485903</v>
+        <v>-2.262194486124497</v>
       </c>
       <c r="G69">
-        <v>-5.126261738590354</v>
+        <v>-4.987715407771854</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.0929643245906</v>
       </c>
       <c r="E70">
-        <v>-8.981605341508697</v>
+        <v>-9.22576707458026</v>
       </c>
       <c r="F70">
-        <v>-2.00702501973354</v>
+        <v>-2.1565892394112</v>
       </c>
       <c r="G70">
-        <v>-4.692053896205084</v>
+        <v>-5.346797040234443</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.48709475969034</v>
       </c>
       <c r="E71">
-        <v>-8.718550814877133</v>
+        <v>-9.861370100874849</v>
       </c>
       <c r="F71">
-        <v>-2.36591933883344</v>
+        <v>-2.649080168132395</v>
       </c>
       <c r="G71">
-        <v>-4.504130778668355</v>
+        <v>-4.792962634787608</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.81876618956045</v>
       </c>
       <c r="E72">
-        <v>-8.700215023620077</v>
+        <v>-8.89321405735298</v>
       </c>
       <c r="F72">
-        <v>-2.278075117603567</v>
+        <v>-2.570452362626069</v>
       </c>
       <c r="G72">
-        <v>-4.814183231694337</v>
+        <v>-4.165127604901446</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.08390708768442</v>
       </c>
       <c r="E73">
-        <v>-8.846733800138251</v>
+        <v>-9.808219401446822</v>
       </c>
       <c r="F73">
-        <v>-2.088812218514144</v>
+        <v>-2.314542335777009</v>
       </c>
       <c r="G73">
-        <v>-4.711526525067077</v>
+        <v>-4.194283579465807</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.28146456948534</v>
       </c>
       <c r="E74">
-        <v>-8.394728695536642</v>
+        <v>-9.275467076814442</v>
       </c>
       <c r="F74">
-        <v>-2.055221091963221</v>
+        <v>-2.606474747504208</v>
       </c>
       <c r="G74">
-        <v>-4.482969771581334</v>
+        <v>-3.801030495946862</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.40759635086828</v>
       </c>
       <c r="E75">
-        <v>-8.567218270488807</v>
+        <v>-10.19048600633031</v>
       </c>
       <c r="F75">
-        <v>-2.363251167429023</v>
+        <v>-2.659444701076223</v>
       </c>
       <c r="G75">
-        <v>-3.670869776979336</v>
+        <v>-3.816407979976776</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.46024178268222</v>
       </c>
       <c r="E76">
-        <v>-9.162590333699251</v>
+        <v>-9.898277164037362</v>
       </c>
       <c r="F76">
-        <v>-2.368399470837422</v>
+        <v>-2.79928223071021</v>
       </c>
       <c r="G76">
-        <v>-3.774132313440283</v>
+        <v>-3.816984014900609</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.4402157885201</v>
       </c>
       <c r="E77">
-        <v>-10.43188084178318</v>
+        <v>-10.56054384528911</v>
       </c>
       <c r="F77">
-        <v>-2.384521157230706</v>
+        <v>-2.743207556112503</v>
       </c>
       <c r="G77">
-        <v>-5.100002491372854</v>
+        <v>-3.529641904274027</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.35428108104766</v>
       </c>
       <c r="E78">
-        <v>-10.22546846803956</v>
+        <v>-10.97462298007648</v>
       </c>
       <c r="F78">
-        <v>-2.452139131586424</v>
+        <v>-2.923900166052562</v>
       </c>
       <c r="G78">
-        <v>-4.555917642539174</v>
+        <v>-3.248152838160877</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-15.21342868407944</v>
       </c>
       <c r="E79">
-        <v>-10.9355467778643</v>
+        <v>-11.48676169102595</v>
       </c>
       <c r="F79">
-        <v>-3.144283171730356</v>
+        <v>-2.988388568360504</v>
       </c>
       <c r="G79">
-        <v>-4.239217614070335</v>
+        <v>-3.05131773203243</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-15.02860953293364</v>
       </c>
       <c r="E80">
-        <v>-11.55781344820629</v>
+        <v>-12.33215533267388</v>
       </c>
       <c r="F80">
-        <v>-3.081331390954608</v>
+        <v>-2.839636977104991</v>
       </c>
       <c r="G80">
-        <v>-3.983785851896788</v>
+        <v>-2.946893194087199</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.81891465173723</v>
       </c>
       <c r="E81">
-        <v>-11.62772402993671</v>
+        <v>-13.02133020647921</v>
       </c>
       <c r="F81">
-        <v>-2.718783971608362</v>
+        <v>-3.183032542098512</v>
       </c>
       <c r="G81">
-        <v>-4.51764111501412</v>
+        <v>-2.68715441216706</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.59895028158222</v>
       </c>
       <c r="E82">
-        <v>-12.63187691334555</v>
+        <v>-13.23332618867429</v>
       </c>
       <c r="F82">
-        <v>-2.998001772069992</v>
+        <v>-2.730010835018504</v>
       </c>
       <c r="G82">
-        <v>-2.875186777706585</v>
+        <v>-2.232719136536844</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.38724972440952</v>
       </c>
       <c r="E83">
-        <v>-14.41537564500045</v>
+        <v>-13.54562787013927</v>
       </c>
       <c r="F83">
-        <v>-3.20859761688371</v>
+        <v>-3.459837308315786</v>
       </c>
       <c r="G83">
-        <v>-2.872568136185021</v>
+        <v>-2.51458891538701</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.19678282618627</v>
       </c>
       <c r="E84">
-        <v>-14.61546626902937</v>
+        <v>-13.82613513559639</v>
       </c>
       <c r="F84">
-        <v>-2.717021205775205</v>
+        <v>-3.159699089096455</v>
       </c>
       <c r="G84">
-        <v>-3.220777937096643</v>
+        <v>-2.77382449438518</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.03424683749054</v>
       </c>
       <c r="E85">
-        <v>-14.58561909684481</v>
+        <v>-15.16299500434877</v>
       </c>
       <c r="F85">
-        <v>-3.161466825134029</v>
+        <v>-3.722954131569201</v>
       </c>
       <c r="G85">
-        <v>-3.527374180579627</v>
+        <v>-2.33207522926145</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.90234008752058</v>
       </c>
       <c r="E86">
-        <v>-15.57353287246215</v>
+        <v>-16.63311427772487</v>
       </c>
       <c r="F86">
-        <v>-3.504453176630567</v>
+        <v>-3.42200494066253</v>
       </c>
       <c r="G86">
-        <v>-3.162780489794152</v>
+        <v>-2.032844949603346</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.79887889715206</v>
       </c>
       <c r="E87">
-        <v>-17.66260850168063</v>
+        <v>-18.11660160637161</v>
       </c>
       <c r="F87">
-        <v>-3.540149184752004</v>
+        <v>-3.643671915814664</v>
       </c>
       <c r="G87">
-        <v>-3.85522743697027</v>
+        <v>-3.101727408958912</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.72376058271282</v>
       </c>
       <c r="E88">
-        <v>-19.2036708488609</v>
+        <v>-18.27022555860782</v>
       </c>
       <c r="F88">
-        <v>-3.549203240464602</v>
+        <v>-3.700353783718623</v>
       </c>
       <c r="G88">
-        <v>-3.208353459687759</v>
+        <v>-2.597438628052811</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.67419511443435</v>
       </c>
       <c r="E89">
-        <v>-20.09731990953457</v>
+        <v>-20.02852333241004</v>
       </c>
       <c r="F89">
-        <v>-3.92249541339256</v>
+        <v>-4.013235607062621</v>
       </c>
       <c r="G89">
-        <v>-3.191655067987675</v>
+        <v>-2.73853076839101</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.65381398570563</v>
       </c>
       <c r="E90">
-        <v>-21.81458518035328</v>
+        <v>-21.86760908250909</v>
       </c>
       <c r="F90">
-        <v>-3.589076705398357</v>
+        <v>-4.145023062276203</v>
       </c>
       <c r="G90">
-        <v>-2.821092463594894</v>
+        <v>-1.905167139790274</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.66560491351327</v>
       </c>
       <c r="E91">
-        <v>-23.36503505415144</v>
+        <v>-22.54831570992008</v>
       </c>
       <c r="F91">
-        <v>-3.67264820756459</v>
+        <v>-3.936025138182484</v>
       </c>
       <c r="G91">
-        <v>-3.134177376334848</v>
+        <v>-2.685346854302618</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.72027386792257</v>
       </c>
       <c r="E92">
-        <v>-25.67715614214373</v>
+        <v>-25.20448308217111</v>
       </c>
       <c r="F92">
-        <v>-4.167446139502583</v>
+        <v>-3.96535597118081</v>
       </c>
       <c r="G92">
-        <v>-3.700800419199887</v>
+        <v>-2.908338580736847</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.82713517525601</v>
       </c>
       <c r="E93">
-        <v>-28.45043438070712</v>
+        <v>-27.07748257411361</v>
       </c>
       <c r="F93">
-        <v>-4.044598425300013</v>
+        <v>-4.322091564829014</v>
       </c>
       <c r="G93">
-        <v>-3.542662279879981</v>
+        <v>-2.753150137492431</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.9920297869149</v>
       </c>
       <c r="E94">
-        <v>-29.30872964480291</v>
+        <v>-29.10495737140576</v>
       </c>
       <c r="F94">
-        <v>-4.15587881708989</v>
+        <v>-4.257319032501912</v>
       </c>
       <c r="G94">
-        <v>-4.038853466397025</v>
+        <v>-3.345178306825837</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.22689361227735</v>
       </c>
       <c r="E95">
-        <v>-31.88787220265748</v>
+        <v>-31.01545715660577</v>
       </c>
       <c r="F95">
-        <v>-3.584796531028092</v>
+        <v>-4.139461403533807</v>
       </c>
       <c r="G95">
-        <v>-3.64791445421003</v>
+        <v>-3.024002420787903</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.54386064321098</v>
       </c>
       <c r="E96">
-        <v>-35.23878220750627</v>
+        <v>-33.11784649940681</v>
       </c>
       <c r="F96">
-        <v>-4.413411615681034</v>
+        <v>-4.415451056226726</v>
       </c>
       <c r="G96">
-        <v>-3.945118679998101</v>
+        <v>-3.715800501038325</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-14.94447388959607</v>
       </c>
       <c r="E97">
-        <v>-35.95586833085788</v>
+        <v>-35.87330745698703</v>
       </c>
       <c r="F97">
-        <v>-4.225884146300476</v>
+        <v>-4.508414588005901</v>
       </c>
       <c r="G97">
-        <v>-3.916674472724682</v>
+        <v>-3.829047642845714</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.43958669975645</v>
       </c>
       <c r="E98">
-        <v>-39.60657916467347</v>
+        <v>-38.32835850584641</v>
       </c>
       <c r="F98">
-        <v>-3.995361095245013</v>
+        <v>-4.24886140131933</v>
       </c>
       <c r="G98">
-        <v>-5.904637205783795</v>
+        <v>-4.291090552125175</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-16.00121622637013</v>
       </c>
       <c r="E99">
-        <v>-42.11690250303347</v>
+        <v>-40.37468081195848</v>
       </c>
       <c r="F99">
-        <v>-4.933975087315702</v>
+        <v>-4.650129198174632</v>
       </c>
       <c r="G99">
-        <v>-5.299145047742173</v>
+        <v>-4.84024053563394</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.64215132135423</v>
       </c>
       <c r="E100">
-        <v>-43.90601427822088</v>
+        <v>-43.48835085625644</v>
       </c>
       <c r="F100">
-        <v>-4.411759022712449</v>
+        <v>-4.820595612527131</v>
       </c>
       <c r="G100">
-        <v>-5.02089038462089</v>
+        <v>-4.91237732293466</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.29130859791988</v>
       </c>
       <c r="E101">
-        <v>-46.55670898963364</v>
+        <v>-44.97085550604351</v>
       </c>
       <c r="F101">
-        <v>-4.350063046919344</v>
+        <v>-4.669570152750934</v>
       </c>
       <c r="G101">
-        <v>-5.302091433272125</v>
+        <v>-4.570801855283738</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.00463050406598</v>
       </c>
       <c r="E102">
-        <v>-49.8192175212602</v>
+        <v>-48.05568143514961</v>
       </c>
       <c r="F102">
-        <v>-4.571881613306191</v>
+        <v>-4.371827572060499</v>
       </c>
       <c r="G102">
-        <v>-5.829689765320234</v>
+        <v>-5.670737231797667</v>
       </c>
     </row>
   </sheetData>
